--- a/REFM_Build_Prompts_v2.1.xlsx
+++ b/REFM_Build_Prompts_v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FMP\financial-modeler-pro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAD4D61-7836-48E5-AE01-FFB0C147822F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4A03F5-C04B-44F6-BE90-E520EB4574F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Architecture" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="562">
   <si>
     <t>REFM Platform: Build Tracker</t>
   </si>
@@ -1265,123 +1265,6 @@
   </si>
   <si>
     <t>Read Architecture sheet sections 1, 1A before starting. Reference Phase M1.5 Module1Hierarchy.tsx for current implementation.</t>
-  </si>
-  <si>
-    <t>Target outcome:</t>
-  </si>
-  <si>
-    <t>1. First-time empty state. When project has zero Sub-Projects (brand new project, just created), show a centered card with:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Title: "Set up your project structure"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Two CTA buttons side by side:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     - "Quick Setup" (primary, navy button) - opens wizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     - "Manual Setup" (secondary, outline button) - shows current Hierarchy tree directly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Brief 1-line description under each button explaining when to use which.</t>
-  </si>
-  <si>
-    <t>2. Quick Setup wizard. Modal-style multi-step form for single-project / single-phase users (90% case):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Step 1: Sub-Project basics (name, currency, location, status)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Step 2: Timeline (construction periods, operations periods, overlap)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Step 3: First Asset (asset type from 20 pre-built dropdown, category auto-derived, allocation %, deduct %, efficiency %)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Step 4: Sub-Units for that asset (skip option for users who want to add later)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Final: "Create" button. Wizard creates Sub-Project + 1 Phase + 1 Asset + Sub-Units (if any) in one transaction.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - User can skip wizard at any step and switch to Manual mode (preserves what's been entered).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Available again later via "Add Sub-Project" button if user wants to add another sub-project via wizard.</t>
-  </si>
-  <si>
-    <t>3. Inline tooltips on each layer label. Hover the layer label or click an info icon to see:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Master Holding: "Optional. Use when you have multiple Sub-Projects under one parent entity (e.g., a real estate fund holding 7 funds, each with own land + debt + returns). Most projects skip this."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Sub-Project: "An independent financing unit. One Sub-Project = one fund / project / standalone development. Has its own equity, debt, returns. Most users have just 1 Sub-Project."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Phase: "A sequenced timeline chunk within a Sub-Project. Most projects have 1 Phase. Add more Phases for staged developments where Phase 2 starts construction years after Phase 1."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Asset: "A building or operating entity. One asset = one building or one operating unit type (e.g., 5-Star Hotel, Branded Apartments Tower 1, Retail Podium)."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Sub-Unit: "Inventory inside an Asset. For Sell: 1BR / 2BR / Branded Suite. For Operate: Twin Key / King Key. For Lease: optional split by floor or zone."</t>
-  </si>
-  <si>
-    <t>4. Visual hierarchy clarity:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Increase indentation per level (currently subtle, needs to be more obvious)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Add expand/collapse chevrons on each level (Sub-Project / Phase / Asset). Default expanded.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Sticky breadcrumb at top when scrolling deep ("FMP Mixed-Used &gt; Phase 1 &gt; Residential")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Subtle background tint per level to reinforce hierarchy (Sub-Project bg navy-pale, Phase bg lighter, Asset bg lightest)</t>
-  </si>
-  <si>
-    <t>5. Empty-state cards at each level when sub-items missing:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Sub-Project with no Phases: "+ Add first Phase" centered card with brief explainer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Phase with no Assets: "+ Add first Asset" centered card with type picker preview</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Asset with no Sub-Units: existing "+ Add Sub-Unit" stays but adds 1-line hint above it</t>
-  </si>
-  <si>
-    <t>6. Page header context. Top of Hierarchy tab adds:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Quick stats line: "1 Sub-Project, 1 Phase, 3 Assets, 0 Sub-Units"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - "Switch to Quick Setup" link (always available, not just empty state)</t>
-  </si>
-  <si>
-    <t>Constraints:</t>
-  </si>
-  <si>
-    <t>- Snapshot diff exit 0 (no calc changes, only UI)</t>
-  </si>
-  <si>
-    <t>- Light + dark mode both work</t>
-  </si>
-  <si>
-    <t>Verification:</t>
-  </si>
-  <si>
-    <t>- Snapshot diff exit 0</t>
-  </si>
-  <si>
-    <t>Split into 4-6 commits, same per-commit verify+push cadence.</t>
   </si>
   <si>
     <t>Polish the Hierarchy tab UX for first-time users. The 5-layer structure is correct but currently feels heavy on first visit.
@@ -1616,6 +1499,446 @@
   </si>
   <si>
     <t>30 to 60 second video walkthrough of 5-layer hierarchy. Embedded in Hierarchy tab empty state. Optional viewing.</t>
+  </si>
+  <si>
+    <t>M1.8</t>
+  </si>
+  <si>
+    <t>Smart Project Creation Wizard</t>
+  </si>
+  <si>
+    <t>3-step wizard at project creation. Asks structure questions (fund/single, phases, plots, project type, assets). Pre-creates hierarchy matching answers. User lands in populated workspace, not empty Hierarchy tab. Progressive disclosure: hidden layers reveal via "+ Add Phase / Plot / Enable Master Holding" buttons.</t>
+  </si>
+  <si>
+    <t>## Purpose</t>
+  </si>
+  <si>
+    <t>Replace the current "blank Hierarchy tab" first experience with a guided wizard that asks 3-5 simple questions and pre-creates the project structure. User lands in a populated workspace, not an empty 5-layer tree.</t>
+  </si>
+  <si>
+    <t>## Problem We Are Solving</t>
+  </si>
+  <si>
+    <t>Current flow: user creates project, lands on Hierarchy tab, sees 5 empty layers (Master Holding, Sub-Project, Phase, Plot, Asset, Sub-Unit), feels overwhelmed.</t>
+  </si>
+  <si>
+    <t>New flow: user answers 3 questions during creation, lands in pre-populated workspace with structure already matching their needs. 90% of users (single project, single phase, single plot, 2-3 assets) never see Master Holding or multi-plot complexity unless they explicitly opt in later.</t>
+  </si>
+  <si>
+    <t>## Reference</t>
+  </si>
+  <si>
+    <t>Read REFM_Build_Prompts_v2.1.xlsx Architecture sheet sections 1, 1A, 2 before starting.</t>
+  </si>
+  <si>
+    <t>## Target Outcome</t>
+  </si>
+  <si>
+    <t>### 1. Replace current "+ New Project" button behavior</t>
+  </si>
+  <si>
+    <t>Currently the New Project button in Projects screen creates an empty project and routes to Hierarchy tab. Change it to open a 3-step wizard modal.</t>
+  </si>
+  <si>
+    <t>### 2. Wizard Step 1: Project Basics</t>
+  </si>
+  <si>
+    <t>Inputs:</t>
+  </si>
+  <si>
+    <t>- Location (required, e.g., "Riyadh, Saudi Arabia")</t>
+  </si>
+  <si>
+    <t>- Model Type (radio: Annual / Monthly, default Annual)</t>
+  </si>
+  <si>
+    <t>- Project Start Date (default today + 6 months)</t>
+  </si>
+  <si>
+    <t>- Status (radio: Draft / Active, default Draft)</t>
+  </si>
+  <si>
+    <t>Validation: Name and location required. Show "Continue" disabled until both filled.</t>
+  </si>
+  <si>
+    <t>### 3. Wizard Step 2: Project Structure</t>
+  </si>
+  <si>
+    <t>Three questions with smart defaults:</t>
+  </si>
+  <si>
+    <t>**Question 1: Is this part of a fund or portfolio?**</t>
+  </si>
+  <si>
+    <t>- If ON: enables Master Holding layer in Hierarchy tab. If OFF: Master Holding hidden by default (user can enable later from Hierarchy tab).</t>
+  </si>
+  <si>
+    <t>**Question 2: How many phases?**</t>
+  </si>
+  <si>
+    <t>- Radio: "Single Phase (most projects)" / "Multiple Phases (staged development)"</t>
+  </si>
+  <si>
+    <t>- Default: Single Phase</t>
+  </si>
+  <si>
+    <t>- If Multiple: ask "How many?" with number input (2-10).</t>
+  </si>
+  <si>
+    <t>**Question 3: How many plots?**</t>
+  </si>
+  <si>
+    <t>- Radio: "Single Plot" / "Multiple Plots (large land bank)"</t>
+  </si>
+  <si>
+    <t>- Default: Single Plot</t>
+  </si>
+  <si>
+    <t>- If Multiple: ask "How many?" with number input (2-20).</t>
+  </si>
+  <si>
+    <t>### 4. Wizard Step 3: Assets</t>
+  </si>
+  <si>
+    <t>Based on user's project type selection, pre-fill suggested assets.</t>
+  </si>
+  <si>
+    <t>**First, ask Project Type:**</t>
+  </si>
+  <si>
+    <t>**Then suggest assets based on type:**</t>
+  </si>
+  <si>
+    <t>| Project Type | Default Assets |</t>
+  </si>
+  <si>
+    <t>|--------------|----------------|</t>
+  </si>
+  <si>
+    <t>| Residential | 1 asset: "Residential Tower" (High-end Apartments, Sell, 100%) |</t>
+  </si>
+  <si>
+    <t>| Hospitality | 1 asset: "Hotel" (Hotel 5-star, Operate, 100%) |</t>
+  </si>
+  <si>
+    <t>| Retail | 1 asset: "Retail Center" (Retail, Lease, 100%) |</t>
+  </si>
+  <si>
+    <t>| Office | 1 asset: "Office Tower" (Office, Lease, 100%) |</t>
+  </si>
+  <si>
+    <t>| Mixed-Use | 3 assets: Residential Tower (Sell, 50%), Hotel (Operate, 30%), Retail Podium (Lease, 20%) |</t>
+  </si>
+  <si>
+    <t>| Custom | Empty list, user adds manually |</t>
+  </si>
+  <si>
+    <t>User can edit/add/remove assets in this step.</t>
+  </si>
+  <si>
+    <t>For each asset row:</t>
+  </si>
+  <si>
+    <t>- Type dropdown (20 pre-built + Custom option)</t>
+  </si>
+  <si>
+    <t>- Category (auto-derived from type, or user-set if Custom)</t>
+  </si>
+  <si>
+    <t>- Allocation % (auto-balances to 100 across all assets)</t>
+  </si>
+  <si>
+    <t>- Remove button (if more than 1 asset)</t>
+  </si>
+  <si>
+    <t>- "+ Add Asset" button below</t>
+  </si>
+  <si>
+    <t>Validation: Total allocation must = 100%. Show "Create Project" disabled until valid.</t>
+  </si>
+  <si>
+    <t>### 5. On "Create Project"</t>
+  </si>
+  <si>
+    <t>Create the project with:</t>
+  </si>
+  <si>
+    <t>- Sub-Project: "Main" (or user-named in Step 1)</t>
+  </si>
+  <si>
+    <t>- Phase 1 (and Phase 2, Phase 3 if user picked Multiple Phases)</t>
+  </si>
+  <si>
+    <t>- Plot 1 (and Plot 2... if user picked Multiple Plots)</t>
+  </si>
+  <si>
+    <t>- Assets pre-created per Step 3 list, all bound to Phase 1 + Plot 1 by default</t>
+  </si>
+  <si>
+    <t>- Single sub-unit per asset auto-created with placeholder values:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - Sell: 1 unit, Unit Size = 100 sqm, Price = 0 (user fills later)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - Operate: 1 key/unit, quantity = 1 (user fills later)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - Lease: 1 area unit, area = 0 (user fills later)</t>
+  </si>
+  <si>
+    <t>- Master Holding: NOT created unless Step 2 Question 1 was ON</t>
+  </si>
+  <si>
+    <t>- Routes to Area Program tab (not Hierarchy tab) since structure is already set up</t>
+  </si>
+  <si>
+    <t>### 6. Hierarchy Tab Polish</t>
+  </si>
+  <si>
+    <t>When Hierarchy tab is opened on a wizard-created project:</t>
+  </si>
+  <si>
+    <t>- Hide layers user said they don't need (Master Holding, multi-phase complexity, multi-plot complexity)</t>
+  </si>
+  <si>
+    <t>- Top of Hierarchy tab: 3 action buttons always visible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - "+ Add Phase" (creates Phase 2, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - "+ Add Plot" (creates Plot 2, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - "Enable Master Holding" toggle (turns on the Master Holding layer if user wants to convert to fund structure later)</t>
+  </si>
+  <si>
+    <t>### 7. Edit Project Structure Later</t>
+  </si>
+  <si>
+    <t>When user clicks "Enable Master Holding" or "+ Add Phase" or "+ Add Plot" later, the new layer appears in Hierarchy tab with empty state guiding them through setup. No re-wizard.</t>
+  </si>
+  <si>
+    <t>## Constraints</t>
+  </si>
+  <si>
+    <t>- Snapshot diffs (legacy + multiphase + areaprogram) must all stay exit 0. No calc changes.</t>
+  </si>
+  <si>
+    <t>- Migrator handles old projects: existing projects without wizard preference flags get default "show all layers" behavior (current behavior preserved).</t>
+  </si>
+  <si>
+    <t>- Light + dark mode both work.</t>
+  </si>
+  <si>
+    <t>- Keyboard navigable (Tab through fields, Enter advances steps).</t>
+  </si>
+  <si>
+    <t>- Esc closes wizard with confirmation if any data entered.</t>
+  </si>
+  <si>
+    <t>- Wizard state preserved if user goes Back to previous step.</t>
+  </si>
+  <si>
+    <t>## Verification</t>
+  </si>
+  <si>
+    <t>1. Snapshot diffs exit 0 (all 3 tracks)</t>
+  </si>
+  <si>
+    <t>2. Type-check + build pass per commit</t>
+  </si>
+  <si>
+    <t>3. Playwright headless test in `tests/e2e/m18-wizard.spec.ts`:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Create project via wizard with default mixed-use selections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Verify project landed on Area Program tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Verify Hierarchy tab shows 3 assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Verify Master Holding layer hidden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Test "Enable Master Holding" reveals layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Test "+ Add Phase" creates Phase 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Screenshots saved to `tests/screenshots/M1.8/` for light + dark</t>
+  </si>
+  <si>
+    <t>4. `scripts/verify-m18.ts`:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Wizard completion creates expected DB rows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Default asset configs match project type matrix above</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   - Existing projects load unchanged</t>
+  </si>
+  <si>
+    <t>## Commit Plan</t>
+  </si>
+  <si>
+    <t>Split into 6-8 commits:</t>
+  </si>
+  <si>
+    <t>1. Wizard component scaffold + 3-step state machine</t>
+  </si>
+  <si>
+    <t>2. Step 1: Project Basics form</t>
+  </si>
+  <si>
+    <t>3. Step 2: Structure questions with conditional fields</t>
+  </si>
+  <si>
+    <t>4. Step 3: Asset list with project-type defaults</t>
+  </si>
+  <si>
+    <t>5. Create-project transactional handler (creates SP + Phase + Plot + Assets + Sub-Units atomically)</t>
+  </si>
+  <si>
+    <t>6. Hierarchy tab progressive disclosure (hide unused layers)</t>
+  </si>
+  <si>
+    <t>7. Hierarchy tab "+ Add Phase / Plot / Enable Master Holding" actions</t>
+  </si>
+  <si>
+    <t>8. Verification scripts + Playwright + screenshots</t>
+  </si>
+  <si>
+    <t>Per-commit cadence: snapshot diff exit 0, type-check + build pass, push to main.</t>
+  </si>
+  <si>
+    <t>When done, report: commit hashes, files touched per commit, verify-m18.ts output, Playwright screenshots path, pattern decisions, deviations.</t>
+  </si>
+  <si>
+    <t>Begin Phase M1.8.</t>
+  </si>
+  <si>
+    <t># Phase M1.8: Smart Project Creation Wizard
+## Purpose
+Replace the current "blank Hierarchy tab" first experience with a guided wizard that asks 3-5 simple questions and pre-creates the project structure. User lands in a populated workspace, not an empty 5-layer tree.
+## Problem We Are Solving
+Current flow: user creates project, lands on Hierarchy tab, sees 5 empty layers (Master Holding, Sub-Project, Phase, Plot, Asset, Sub-Unit), feels overwhelmed.
+New flow: user answers 3 questions during creation, lands in pre-populated workspace with structure already matching their needs. 90% of users (single project, single phase, single plot, 2-3 assets) never see Master Holding or multi-plot complexity unless they explicitly opt in later.
+## Reference
+Read REFM_Build_Prompts_v2.1.xlsx Architecture sheet sections 1, 1A, 2 before starting.
+## Target Outcome
+### 1. Replace current "+ New Project" button behavior
+Currently the New Project button in Projects screen creates an empty project and routes to Hierarchy tab. Change it to open a 3-step wizard modal.
+### 2. Wizard Step 1: Project Basics
+Inputs:
+- Project Name (required)
+- Location (required, e.g., "Riyadh, Saudi Arabia")
+- Currency (default SAR, dropdown from common currencies)
+- Model Type (radio: Annual / Monthly, default Annual)
+- Project Start Date (default today + 6 months)
+- Status (radio: Draft / Active, default Draft)
+Validation: Name and location required. Show "Continue" disabled until both filled.
+### 3. Wizard Step 2: Project Structure
+Three questions with smart defaults:
+**Question 1: Is this part of a fund or portfolio?**
+- Toggle (default OFF)
+- If ON: enables Master Holding layer in Hierarchy tab. If OFF: Master Holding hidden by default (user can enable later from Hierarchy tab).
+**Question 2: How many phases?**
+- Radio: "Single Phase (most projects)" / "Multiple Phases (staged development)"
+- Default: Single Phase
+- If Multiple: ask "How many?" with number input (2-10).
+**Question 3: How many plots?**
+- Radio: "Single Plot" / "Multiple Plots (large land bank)"
+- Default: Single Plot
+- If Multiple: ask "How many?" with number input (2-20).
+### 4. Wizard Step 3: Assets
+Based on user's project type selection, pre-fill suggested assets.
+**First, ask Project Type:**
+- Radio: Residential / Hospitality / Retail / Mixed-Use / Office / Custom
+- Default: Mixed-Use
+**Then suggest assets based on type:**
+| Project Type | Default Assets |
+|--------------|----------------|
+| Residential | 1 asset: "Residential Tower" (High-end Apartments, Sell, 100%) |
+| Hospitality | 1 asset: "Hotel" (Hotel 5-star, Operate, 100%) |
+| Retail | 1 asset: "Retail Center" (Retail, Lease, 100%) |
+| Office | 1 asset: "Office Tower" (Office, Lease, 100%) |
+| Mixed-Use | 3 assets: Residential Tower (Sell, 50%), Hotel (Operate, 30%), Retail Podium (Lease, 20%) |
+| Custom | Empty list, user adds manually |
+User can edit/add/remove assets in this step.
+For each asset row:
+- Name (editable)
+- Type dropdown (20 pre-built + Custom option)
+- Category (auto-derived from type, or user-set if Custom)
+- Allocation % (auto-balances to 100 across all assets)
+- Remove button (if more than 1 asset)
+- "+ Add Asset" button below
+Validation: Total allocation must = 100%. Show "Create Project" disabled until valid.
+### 5. On "Create Project"
+Create the project with:
+- Sub-Project: "Main" (or user-named in Step 1)
+- Phase 1 (and Phase 2, Phase 3 if user picked Multiple Phases)
+- Plot 1 (and Plot 2... if user picked Multiple Plots)
+- Assets pre-created per Step 3 list, all bound to Phase 1 + Plot 1 by default
+- Single sub-unit per asset auto-created with placeholder values:
+  - Sell: 1 unit, Unit Size = 100 sqm, Price = 0 (user fills later)
+  - Operate: 1 key/unit, quantity = 1 (user fills later)
+  - Lease: 1 area unit, area = 0 (user fills later)
+- Master Holding: NOT created unless Step 2 Question 1 was ON
+- Routes to Area Program tab (not Hierarchy tab) since structure is already set up
+### 6. Hierarchy Tab Polish
+When Hierarchy tab is opened on a wizard-created project:
+- Hide layers user said they don't need (Master Holding, multi-phase complexity, multi-plot complexity)
+- Show only their actual structure
+- Top of Hierarchy tab: 3 action buttons always visible
+  - "+ Add Phase" (creates Phase 2, etc.)
+  - "+ Add Plot" (creates Plot 2, etc.)
+  - "Enable Master Holding" toggle (turns on the Master Holding layer if user wants to convert to fund structure later)
+### 7. Edit Project Structure Later
+When user clicks "Enable Master Holding" or "+ Add Phase" or "+ Add Plot" later, the new layer appears in Hierarchy tab with empty state guiding them through setup. No re-wizard.
+## Constraints
+- Snapshot diffs (legacy + multiphase + areaprogram) must all stay exit 0. No calc changes.
+- Migrator handles old projects: existing projects without wizard preference flags get default "show all layers" behavior (current behavior preserved).
+- FAST cells throughout wizard.
+- Light + dark mode both work.
+- Keyboard navigable (Tab through fields, Enter advances steps).
+- Esc closes wizard with confirmation if any data entered.
+- Wizard state preserved if user goes Back to previous step.
+## Verification
+1. Snapshot diffs exit 0 (all 3 tracks)
+2. Type-check + build pass per commit
+3. Playwright headless test in `tests/e2e/m18-wizard.spec.ts`:
+   - Create project via wizard with default mixed-use selections
+   - Verify project landed on Area Program tab
+   - Verify Hierarchy tab shows 3 assets
+   - Verify Master Holding layer hidden
+   - Test "Enable Master Holding" reveals layer
+   - Test "+ Add Phase" creates Phase 2
+   - Screenshots saved to `tests/screenshots/M1.8/` for light + dark
+4. `scripts/verify-m18.ts`:
+   - Wizard completion creates expected DB rows
+   - Default asset configs match project type matrix above
+   - Existing projects load unchanged
+## Commit Plan
+Split into 6-8 commits:
+1. Wizard component scaffold + 3-step state machine
+2. Step 1: Project Basics form
+3. Step 2: Structure questions with conditional fields
+4. Step 3: Asset list with project-type defaults
+5. Create-project transactional handler (creates SP + Phase + Plot + Assets + Sub-Units atomically)
+6. Hierarchy tab progressive disclosure (hide unused layers)
+7. Hierarchy tab "+ Add Phase / Plot / Enable Master Holding" actions
+8. Verification scripts + Playwright + screenshots
+Per-commit cadence: snapshot diff exit 0, type-check + build pass, push to main.
+When done, report: commit hashes, files touched per commit, verify-m18.ts output, Playwright screenshots path, pattern decisions, deviations.
+Begin Phase M1.8.</t>
   </si>
 </sst>
 </file>
@@ -1952,20 +2275,23 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1990,23 +2316,20 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2380,22 +2703,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="28.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="56" t="s">
         <v>194</v>
       </c>
-      <c r="C1" s="54"/>
+      <c r="C1" s="55"/>
     </row>
     <row r="2" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="C2" s="54"/>
+      <c r="C2" s="55"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="51" t="s">
         <v>196</v>
       </c>
-      <c r="C4" s="51"/>
+      <c r="C4" s="52"/>
     </row>
     <row r="5" spans="2:3" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
@@ -2454,10 +2777,10 @@
       </c>
     </row>
     <row r="13" spans="2:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="56" t="s">
+      <c r="B13" s="57" t="s">
         <v>210</v>
       </c>
-      <c r="C13" s="57"/>
+      <c r="C13" s="58"/>
     </row>
     <row r="14" spans="2:3" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="28" t="s">
@@ -2500,10 +2823,10 @@
       </c>
     </row>
     <row r="19" spans="2:3" ht="97.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="52" t="s">
+      <c r="B19" s="53" t="s">
         <v>221</v>
       </c>
-      <c r="C19" s="53" t="s">
+      <c r="C19" s="54" t="s">
         <v>222</v>
       </c>
     </row>
@@ -2530,10 +2853,10 @@
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B23" s="48" t="s">
+      <c r="B23" s="49" t="s">
         <v>228</v>
       </c>
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="50" t="s">
         <v>229</v>
       </c>
     </row>
@@ -2577,8 +2900,8 @@
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B30" s="54"/>
-      <c r="C30" s="54"/>
+      <c r="B30" s="55"/>
+      <c r="C30" s="55"/>
     </row>
     <row r="31" spans="2:3" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="26" t="s">
@@ -2627,10 +2950,10 @@
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B38" s="50" t="s">
+      <c r="B38" s="51" t="s">
         <v>250</v>
       </c>
-      <c r="C38" s="51"/>
+      <c r="C38" s="52"/>
     </row>
     <row r="39" spans="2:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
@@ -2712,10 +3035,10 @@
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B50" s="48" t="s">
+      <c r="B50" s="49" t="s">
         <v>269</v>
       </c>
-      <c r="C50" s="49" t="s">
+      <c r="C50" s="50" t="s">
         <v>270</v>
       </c>
     </row>
@@ -2760,10 +3083,10 @@
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B56" s="48" t="s">
+      <c r="B56" s="49" t="s">
         <v>281</v>
       </c>
-      <c r="C56" s="49" t="s">
+      <c r="C56" s="50" t="s">
         <v>282</v>
       </c>
     </row>
@@ -2807,8 +3130,8 @@
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B63" s="54"/>
-      <c r="C63" s="54"/>
+      <c r="B63" s="55"/>
+      <c r="C63" s="55"/>
     </row>
     <row r="64" spans="2:3" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="26" t="s">
@@ -2849,10 +3172,10 @@
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B69" s="48" t="s">
+      <c r="B69" s="49" t="s">
         <v>301</v>
       </c>
-      <c r="C69" s="49" t="s">
+      <c r="C69" s="50" t="s">
         <v>302</v>
       </c>
     </row>
@@ -2896,8 +3219,8 @@
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B76" s="54"/>
-      <c r="C76" s="54"/>
+      <c r="B76" s="55"/>
+      <c r="C76" s="55"/>
     </row>
     <row r="77" spans="2:3" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="26" t="s">
@@ -2946,10 +3269,10 @@
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B84" s="50" t="s">
+      <c r="B84" s="51" t="s">
         <v>323</v>
       </c>
-      <c r="C84" s="51"/>
+      <c r="C84" s="52"/>
     </row>
     <row r="85" spans="2:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
@@ -2992,10 +3315,10 @@
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B90" s="48" t="s">
+      <c r="B90" s="49" t="s">
         <v>334</v>
       </c>
-      <c r="C90" s="49" t="s">
+      <c r="C90" s="50" t="s">
         <v>335</v>
       </c>
     </row>
@@ -3023,10 +3346,10 @@
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B95" s="48" t="s">
+      <c r="B95" s="49" t="s">
         <v>341</v>
       </c>
-      <c r="C95" s="49" t="s">
+      <c r="C95" s="50" t="s">
         <v>342</v>
       </c>
     </row>
@@ -3054,10 +3377,10 @@
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B100" s="48" t="s">
+      <c r="B100" s="49" t="s">
         <v>348</v>
       </c>
-      <c r="C100" s="49" t="s">
+      <c r="C100" s="50" t="s">
         <v>349</v>
       </c>
     </row>
@@ -3180,7 +3503,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:K59"/>
+  <dimension ref="B1:K60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" style="6" customWidth="1"/>
@@ -3196,31 +3519,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
+      <c r="B1" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
       <c r="K1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
       <c r="K2" s="6" t="s">
         <v>3</v>
       </c>
@@ -3551,7 +3874,7 @@
         <v>56</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F18" s="23">
         <v>46144</v>
@@ -3566,37 +3889,37 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="126" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="10" t="s">
+    <row r="19" spans="2:9" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="30" t="s">
+        <v>453</v>
+      </c>
+      <c r="C19" t="s">
+        <v>454</v>
+      </c>
+      <c r="D19" s="29" t="s">
+        <v>455</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="31">
+        <v>8</v>
+      </c>
+      <c r="I19" s="29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="126" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C20" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D20" s="11" t="s">
         <v>59</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="12">
-        <v>14</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>62</v>
       </c>
       <c r="E20" s="16" t="s">
         <v>53</v>
@@ -3604,21 +3927,21 @@
       <c r="F20" s="24"/>
       <c r="G20" s="24"/>
       <c r="H20" s="12">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I20" s="11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E21" s="16" t="s">
         <v>53</v>
@@ -3626,21 +3949,21 @@
       <c r="F21" s="24"/>
       <c r="G21" s="24"/>
       <c r="H21" s="12">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I21" s="11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>53</v>
@@ -3651,18 +3974,18 @@
         <v>6</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E23" s="16" t="s">
         <v>53</v>
@@ -3670,21 +3993,21 @@
       <c r="F23" s="24"/>
       <c r="G23" s="24"/>
       <c r="H23" s="12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E24" s="16" t="s">
         <v>53</v>
@@ -3692,21 +4015,21 @@
       <c r="F24" s="24"/>
       <c r="G24" s="24"/>
       <c r="H24" s="12">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E25" s="16" t="s">
         <v>53</v>
@@ -3714,21 +4037,21 @@
       <c r="F25" s="24"/>
       <c r="G25" s="24"/>
       <c r="H25" s="12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E26" s="16" t="s">
         <v>53</v>
@@ -3736,21 +4059,21 @@
       <c r="F26" s="24"/>
       <c r="G26" s="24"/>
       <c r="H26" s="12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E27" s="16" t="s">
         <v>53</v>
@@ -3761,18 +4084,18 @@
         <v>6</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>53</v>
@@ -3780,21 +4103,21 @@
       <c r="F28" s="24"/>
       <c r="G28" s="24"/>
       <c r="H28" s="12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I28" s="11" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E29" s="16" t="s">
         <v>53</v>
@@ -3808,15 +4131,15 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="2:9" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E30" s="16" t="s">
         <v>53</v>
@@ -3830,15 +4153,15 @@
         <v>81</v>
       </c>
     </row>
-    <row r="31" spans="2:9" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:9" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E31" s="16" t="s">
         <v>53</v>
@@ -3846,21 +4169,21 @@
       <c r="F31" s="24"/>
       <c r="G31" s="24"/>
       <c r="H31" s="12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="10" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>53</v>
@@ -3871,18 +4194,18 @@
         <v>6</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="10" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E33" s="16" t="s">
         <v>53</v>
@@ -3893,18 +4216,18 @@
         <v>6</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E34" s="16" t="s">
         <v>53</v>
@@ -3912,21 +4235,21 @@
       <c r="F34" s="24"/>
       <c r="G34" s="24"/>
       <c r="H34" s="12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I34" s="11" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E35" s="16" t="s">
         <v>53</v>
@@ -3934,21 +4257,21 @@
       <c r="F35" s="24"/>
       <c r="G35" s="24"/>
       <c r="H35" s="12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E36" s="16" t="s">
         <v>53</v>
@@ -3959,18 +4282,18 @@
         <v>8</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E37" s="16" t="s">
         <v>53</v>
@@ -3978,21 +4301,21 @@
       <c r="F37" s="24"/>
       <c r="G37" s="24"/>
       <c r="H37" s="12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="2:9" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E38" s="16" t="s">
         <v>53</v>
@@ -4003,18 +4326,18 @@
         <v>6</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E39" s="16" t="s">
         <v>53</v>
@@ -4022,21 +4345,21 @@
       <c r="F39" s="24"/>
       <c r="G39" s="24"/>
       <c r="H39" s="12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E40" s="16" t="s">
         <v>53</v>
@@ -4044,21 +4367,21 @@
       <c r="F40" s="24"/>
       <c r="G40" s="24"/>
       <c r="H40" s="12">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E41" s="16" t="s">
         <v>53</v>
@@ -4066,21 +4389,21 @@
       <c r="F41" s="24"/>
       <c r="G41" s="24"/>
       <c r="H41" s="12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E42" s="16" t="s">
         <v>53</v>
@@ -4091,18 +4414,18 @@
         <v>8</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>131</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E43" s="16" t="s">
         <v>53</v>
@@ -4110,65 +4433,65 @@
       <c r="F43" s="24"/>
       <c r="G43" s="24"/>
       <c r="H43" s="12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="44" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="10" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>143</v>
+        <v>53</v>
       </c>
       <c r="F44" s="24"/>
       <c r="G44" s="24"/>
       <c r="H44" s="12">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="10" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>53</v>
+        <v>143</v>
       </c>
       <c r="F45" s="24"/>
       <c r="G45" s="24"/>
       <c r="H45" s="12">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="10" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E46" s="16" t="s">
         <v>53</v>
@@ -4176,21 +4499,21 @@
       <c r="F46" s="24"/>
       <c r="G46" s="24"/>
       <c r="H46" s="12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="10" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E47" s="16" t="s">
         <v>53</v>
@@ -4198,21 +4521,21 @@
       <c r="F47" s="24"/>
       <c r="G47" s="24"/>
       <c r="H47" s="12">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="10" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E48" s="16" t="s">
         <v>53</v>
@@ -4220,21 +4543,21 @@
       <c r="F48" s="24"/>
       <c r="G48" s="24"/>
       <c r="H48" s="12">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="49" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="10" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E49" s="16" t="s">
         <v>53</v>
@@ -4242,21 +4565,21 @@
       <c r="F49" s="24"/>
       <c r="G49" s="24"/>
       <c r="H49" s="12">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="50" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="10" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E50" s="16" t="s">
         <v>53</v>
@@ -4264,21 +4587,21 @@
       <c r="F50" s="24"/>
       <c r="G50" s="24"/>
       <c r="H50" s="12">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="51" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="10" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E51" s="16" t="s">
         <v>53</v>
@@ -4286,21 +4609,21 @@
       <c r="F51" s="24"/>
       <c r="G51" s="24"/>
       <c r="H51" s="12">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E52" s="16" t="s">
         <v>53</v>
@@ -4308,21 +4631,21 @@
       <c r="F52" s="24"/>
       <c r="G52" s="24"/>
       <c r="H52" s="12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="53" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="10" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E53" s="16" t="s">
         <v>53</v>
@@ -4336,15 +4659,15 @@
         <v>173</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="10" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E54" s="16" t="s">
         <v>53</v>
@@ -4352,7 +4675,7 @@
       <c r="F54" s="24"/>
       <c r="G54" s="24"/>
       <c r="H54" s="12">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I54" s="11" t="s">
         <v>173</v>
@@ -4360,13 +4683,13 @@
     </row>
     <row r="55" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="10" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E55" s="16" t="s">
         <v>53</v>
@@ -4374,21 +4697,21 @@
       <c r="F55" s="24"/>
       <c r="G55" s="24"/>
       <c r="H55" s="12">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
     </row>
     <row r="56" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="10" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E56" s="16" t="s">
         <v>53</v>
@@ -4396,21 +4719,21 @@
       <c r="F56" s="24"/>
       <c r="G56" s="24"/>
       <c r="H56" s="12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="10" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E57" s="16" t="s">
         <v>53</v>
@@ -4418,21 +4741,21 @@
       <c r="F57" s="24"/>
       <c r="G57" s="24"/>
       <c r="H57" s="12">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="58" spans="2:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="10" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E58" s="16" t="s">
         <v>53</v>
@@ -4440,25 +4763,47 @@
       <c r="F58" s="24"/>
       <c r="G58" s="24"/>
       <c r="H58" s="12">
+        <v>12</v>
+      </c>
+      <c r="I58" s="11" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="E59" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F59" s="24"/>
+      <c r="G59" s="24"/>
+      <c r="H59" s="12">
         <v>4</v>
       </c>
-      <c r="I58" s="11" t="s">
+      <c r="I59" s="11" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B59" s="4"/>
-      <c r="C59" s="4" t="s">
+    <row r="60" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B60" s="4"/>
+      <c r="C60" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="D59" s="4"/>
-      <c r="E59" s="17"/>
-      <c r="F59" s="25"/>
-      <c r="G59" s="25"/>
-      <c r="H59" s="5">
+      <c r="D60" s="4"/>
+      <c r="E60" s="17"/>
+      <c r="F60" s="25"/>
+      <c r="G60" s="25"/>
+      <c r="H60" s="5">
         <v>348</v>
       </c>
-      <c r="I59" s="4"/>
+      <c r="I60" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4477,7 +4822,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E57" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E58" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>$K$1:$K$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -4487,7 +4832,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:G63"/>
+  <dimension ref="B1:G164"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" style="6" customWidth="1"/>
@@ -4501,18 +4846,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="60" t="s">
         <v>372</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
     </row>
     <row r="2" spans="2:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="64" t="s">
         <v>373</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
     </row>
     <row r="4" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
@@ -4588,7 +4933,7 @@
         <v>387</v>
       </c>
       <c r="D7" s="42" t="s">
-        <v>429</v>
+        <v>390</v>
       </c>
       <c r="E7" s="15" t="str">
         <f>Tracker!E16</f>
@@ -4636,7 +4981,7 @@
       </c>
       <c r="E9" s="15" t="str">
         <f>Tracker!E18</f>
-        <v>In Progress</v>
+        <v xml:space="preserve">Done </v>
       </c>
       <c r="F9" s="35">
         <f>Tracker!F18</f>
@@ -4648,16 +4993,18 @@
       </c>
     </row>
     <row r="10" spans="2:7" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>377</v>
-      </c>
-      <c r="D10" s="20"/>
+      <c r="B10" s="32" t="s">
+        <v>453</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>454</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>561</v>
+      </c>
       <c r="E10" s="15" t="str">
         <f>Tracker!E19</f>
-        <v>Not started</v>
+        <v>Not Started</v>
       </c>
       <c r="F10" s="35">
         <f>Tracker!F19</f>
@@ -4670,14 +5017,12 @@
     </row>
     <row r="11" spans="2:7" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="18" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>378</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>390</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="D11" s="20"/>
       <c r="E11" s="15" t="str">
         <f>Tracker!E20</f>
         <v>Not started</v>
@@ -4691,14 +5036,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="364.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="18" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>379</v>
-      </c>
-      <c r="D12" s="20"/>
+        <v>378</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>456</v>
+      </c>
       <c r="E12" s="15" t="str">
         <f>Tracker!E21</f>
         <v>Not started</v>
@@ -4712,16 +5059,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="252" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" ht="364.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="18" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>380</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>391</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="D13" s="20"/>
       <c r="E13" s="15" t="str">
         <f>Tracker!E22</f>
         <v>Not started</v>
@@ -4735,15 +5080,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="238.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" ht="252" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="18" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>71</v>
+        <v>380</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>392</v>
+        <v>457</v>
       </c>
       <c r="E14" s="15" t="str">
         <f>Tracker!E23</f>
@@ -4758,16 +5103,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="265.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" ht="238.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="18" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>381</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>393</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="D15" s="20"/>
       <c r="E15" s="15" t="str">
         <f>Tracker!E24</f>
         <v>Not started</v>
@@ -4781,15 +5124,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="391.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" ht="265.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>78</v>
+        <v>381</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>394</v>
+        <v>458</v>
       </c>
       <c r="E16" s="15" t="str">
         <f>Tracker!E25</f>
@@ -4804,16 +5147,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="265.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" ht="391.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="18" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>395</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="D17" s="20"/>
       <c r="E17" s="15" t="str">
         <f>Tracker!E26</f>
         <v>Not started</v>
@@ -4827,15 +5168,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="238.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" ht="265.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="18" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>396</v>
+        <v>459</v>
       </c>
       <c r="E18" s="15" t="str">
         <f>Tracker!E27</f>
@@ -4850,12 +5191,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="223.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:7" ht="238.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="18" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D19" s="20"/>
       <c r="E19" s="15" t="str">
@@ -4871,15 +5212,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="265.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" ht="223.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="18" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>382</v>
+        <v>89</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>397</v>
+        <v>460</v>
       </c>
       <c r="E20" s="15" t="str">
         <f>Tracker!E29</f>
@@ -4894,16 +5235,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="307.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" ht="265.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>398</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="D21" s="20"/>
       <c r="E21" s="15" t="str">
         <f>Tracker!E30</f>
         <v>Not started</v>
@@ -4917,15 +5256,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="196.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:7" ht="307.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="18" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>383</v>
+        <v>95</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>399</v>
+        <v>461</v>
       </c>
       <c r="E22" s="15" t="str">
         <f>Tracker!E31</f>
@@ -4940,16 +5279,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="181.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:7" ht="196.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="18" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>384</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>400</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="D23" s="20"/>
       <c r="E23" s="15" t="str">
         <f>Tracker!E32</f>
         <v>Not started</v>
@@ -4963,15 +5300,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="168" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:7" ht="181.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="18" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>105</v>
+        <v>384</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>401</v>
+        <v>462</v>
       </c>
       <c r="E24" s="15" t="str">
         <f>Tracker!E33</f>
@@ -4986,16 +5323,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="223.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:7" ht="168" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="18" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>385</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>402</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="D25" s="20"/>
       <c r="E25" s="15" t="str">
         <f>Tracker!E34</f>
         <v>Not started</v>
@@ -5009,15 +5344,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="294" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:7" ht="223.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="18" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>111</v>
+        <v>385</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>403</v>
+        <v>463</v>
       </c>
       <c r="E26" s="15" t="str">
         <f>Tracker!E35</f>
@@ -5032,16 +5367,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="181.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:7" ht="294" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="18" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>404</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="D27" s="20"/>
       <c r="E27" s="15" t="str">
         <f>Tracker!E36</f>
         <v>Not started</v>
@@ -5055,14 +5388,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="196.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:7" ht="181.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="18" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D28" s="20"/>
+        <v>115</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>464</v>
+      </c>
       <c r="E28" s="15" t="str">
         <f>Tracker!E37</f>
         <v>Not started</v>
@@ -5076,16 +5411,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="265.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:7" ht="196.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="18" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>405</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="D29" s="20"/>
       <c r="E29" s="15" t="str">
         <f>Tracker!E38</f>
         <v>Not started</v>
@@ -5099,15 +5432,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="154.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:7" ht="265.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="18" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>406</v>
+        <v>465</v>
       </c>
       <c r="E30" s="15" t="str">
         <f>Tracker!E39</f>
@@ -5122,16 +5455,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:7" ht="294" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:7" ht="154.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="18" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="D31" s="20" t="s">
-        <v>407</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="D31" s="20"/>
       <c r="E31" s="15" t="str">
         <f>Tracker!E40</f>
         <v>Not started</v>
@@ -5145,15 +5476,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:7" ht="210" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:7" ht="294" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="18" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>408</v>
+        <v>466</v>
       </c>
       <c r="E32" s="15" t="str">
         <f>Tracker!E41</f>
@@ -5168,16 +5499,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:7" ht="223.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:7" ht="210" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="18" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>409</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D33" s="20"/>
       <c r="E33" s="15" t="str">
         <f>Tracker!E42</f>
         <v>Not started</v>
@@ -5191,15 +5520,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:7" ht="280.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:7" ht="223.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="18" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>410</v>
+        <v>467</v>
       </c>
       <c r="E34" s="15" t="str">
         <f>Tracker!E43</f>
@@ -5216,15 +5545,18 @@
     </row>
     <row r="35" spans="2:7" ht="280.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="18" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D35" s="20"/>
+        <v>138</v>
+      </c>
+      <c r="D35" s="20" t="e" cm="1">
+        <f t="array" ref="D35">- project Name (required)</f>
+        <v>#NAME?</v>
+      </c>
       <c r="E35" s="15" t="str">
         <f>Tracker!E44</f>
-        <v>Optional v1.5</v>
+        <v>Not started</v>
       </c>
       <c r="F35" s="35">
         <f>Tracker!F44</f>
@@ -5235,19 +5567,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:7" ht="168" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:7" ht="280.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="18" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D36" s="20" t="s">
-        <v>411</v>
+        <v>468</v>
       </c>
       <c r="E36" s="15" t="str">
         <f>Tracker!E45</f>
-        <v>Not started</v>
+        <v>Optional v1.5</v>
       </c>
       <c r="F36" s="35">
         <f>Tracker!F45</f>
@@ -5258,15 +5590,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:7" ht="265.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:7" ht="168" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="18" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>412</v>
+        <v>150</v>
+      </c>
+      <c r="D37" s="20" t="e" cm="1">
+        <f t="array" ref="D37">- Currency (default SAR, dropdown from common currencies)</f>
+        <v>#NAME?</v>
       </c>
       <c r="E37" s="15" t="str">
         <f>Tracker!E46</f>
@@ -5281,15 +5614,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:7" ht="265.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="18" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D38" s="20" t="s">
-        <v>413</v>
+        <v>469</v>
       </c>
       <c r="E38" s="15" t="str">
         <f>Tracker!E47</f>
@@ -5304,15 +5637,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:7" ht="238.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:7" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="18" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="E39" s="15" t="str">
         <f>Tracker!E48</f>
@@ -5327,15 +5660,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:7" ht="154.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:7" ht="238.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="18" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D40" s="20" t="s">
-        <v>415</v>
+        <v>471</v>
       </c>
       <c r="E40" s="15" t="str">
         <f>Tracker!E49</f>
@@ -5350,12 +5683,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:7" ht="322.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:7" ht="154.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="18" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D41" s="20"/>
       <c r="E41" s="15" t="str">
@@ -5371,15 +5704,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:7" ht="265.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:7" ht="322.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="18" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D42" s="20" t="s">
-        <v>416</v>
+        <v>472</v>
       </c>
       <c r="E42" s="15" t="str">
         <f>Tracker!E51</f>
@@ -5394,16 +5727,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:7" ht="294" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:7" ht="265.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="18" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>417</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="D43" s="20"/>
       <c r="E43" s="15" t="str">
         <f>Tracker!E52</f>
         <v>Not started</v>
@@ -5417,15 +5748,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:7" ht="181.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:7" ht="294" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="18" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D44" s="20" t="s">
-        <v>418</v>
+        <v>473</v>
       </c>
       <c r="E44" s="15" t="str">
         <f>Tracker!E53</f>
@@ -5440,16 +5771,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:7" ht="223.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:7" ht="181.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="18" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>419</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="D45" s="20"/>
       <c r="E45" s="15" t="str">
         <f>Tracker!E54</f>
         <v>Not started</v>
@@ -5465,12 +5794,14 @@
     </row>
     <row r="46" spans="2:7" ht="223.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="18" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="D46" s="20"/>
+        <v>181</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>474</v>
+      </c>
       <c r="E46" s="15" t="str">
         <f>Tracker!E55</f>
         <v>Not started</v>
@@ -5484,16 +5815,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:7" ht="168" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:7" ht="223.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="18" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>420</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="D47" s="20"/>
       <c r="E47" s="15" t="str">
         <f>Tracker!E56</f>
         <v>Not started</v>
@@ -5507,15 +5836,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:7" ht="168" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="18" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>421</v>
+        <v>475</v>
       </c>
       <c r="E48" s="15" t="str">
         <f>Tracker!E57</f>
@@ -5530,69 +5859,483 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D49" s="6" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="51" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D51" s="6" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="52" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B49" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="D49" s="20" t="e" cm="1">
+        <f t="array" ref="D49">- Toggle (default OFF)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="E49" s="15" t="str">
+        <f>Tracker!E58</f>
+        <v>Not started</v>
+      </c>
+      <c r="F49" s="35">
+        <f>Tracker!F58</f>
+        <v>0</v>
+      </c>
+      <c r="G49" s="35">
+        <f>Tracker!G58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D50" s="6" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
       <c r="D52" s="6" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="53" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D53" s="6" t="e" cm="1">
-        <f t="array" ref="D53">- _xleta.TYPE-check + build pass</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="54" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D54" s="6" t="e" cm="1">
-        <f t="array" ref="D54">- FAST cells throughout (no hardcoded colors)</f>
+        <v>477</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D53" s="6" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D54" s="6" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D55" s="6" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D57" s="6" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D58" s="6" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D59" s="6" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D60" s="6" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D62" s="6" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D64" s="6" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="66" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D66" s="6" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="67" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D67" s="6" t="e" cm="1">
+        <f t="array" ref="D67">- radio: Residential / Hospitality / Retail / Mixed-use / Office / Custom</f>
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="55" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D55" s="6" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="56" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D56" s="6" t="e" cm="1">
-        <f t="array" ref="D56">- Keyboard navigable (tab through wizard steps, Esc to close)</f>
+    <row r="68" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D68" s="6" t="e" cm="1">
+        <f t="array" ref="D68">- default: Mixed-use</f>
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="57" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D57" s="6" t="e" cm="1">
-        <f t="array" ref="D57">- Accessible: tooltips have aria-label, wizard is screen-reader friendly</f>
+    <row r="70" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D70" s="6" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="72" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D72" s="6" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="73" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D73" s="6" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="74" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D74" s="6" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="75" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D75" s="6" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="76" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D76" s="6" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="77" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D77" s="6" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="78" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D78" s="6" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="79" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D79" s="6" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="81" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D81" s="6" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="83" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D83" s="6" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="84" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D84" s="6" t="e" cm="1">
+        <f t="array" ref="D84">- Name (editable)</f>
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="59" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D59" s="6" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="60" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D60" s="6" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="61" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D61" s="6" t="e" cm="1">
-        <f t="array" ref="D61">- Eyeball: create new project, walk through Quick Setup wizard end-to-end. Then create another project, use Manual Setup. Then open existing migrated project, verify breadcrumb + indentation + tooltips read correctly.</f>
+    <row r="85" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D85" s="6" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="86" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D86" s="6" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="87" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D87" s="6" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="88" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D88" s="6" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="89" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D89" s="6" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="91" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D91" s="6" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="93" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D93" s="6" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="95" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D95" s="6" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="96" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D96" s="6" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="97" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D97" s="6" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="98" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D98" s="6" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="99" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D99" s="6" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="100" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D100" s="6" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="101" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D101" s="6" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="102" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D102" s="6" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="103" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D103" s="6" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="104" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D104" s="6" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="105" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D105" s="6" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="107" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D107" s="6" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="109" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D109" s="6" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="110" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D110" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="111" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D111" s="6" t="e" cm="1">
+        <f t="array" ref="D111">- Show only their actual structure</f>
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="63" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D63" s="6" t="s">
-        <v>428</v>
+    <row r="112" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D112" s="6" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="113" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D113" s="6" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="114" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D114" s="6" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="115" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D115" s="6" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="117" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D117" s="6" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="119" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D119" s="6" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="121" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D121" s="6" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="123" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D123" s="6" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="124" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D124" s="6" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="125" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D125" s="6" t="e" cm="1">
+        <f t="array" ref="D125">- FAST cells throughout wizard.</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="126" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D126" s="6" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="127" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D127" s="6" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="128" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D128" s="6" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="129" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D129" s="6" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="131" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D131" s="6" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="133" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D133" s="6" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="134" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D134" s="6" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="135" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D135" s="6" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="136" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D136" s="6" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="137" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D137" s="6" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="138" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D138" s="6" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="139" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D139" s="6" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="140" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D140" s="6" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="141" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D141" s="6" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="142" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D142" s="6" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="143" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D143" s="6" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="144" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D144" s="6" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="145" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D145" s="6" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="146" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D146" s="6" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="148" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D148" s="6" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="150" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D150" s="6" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="151" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D151" s="6" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="152" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D152" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="153" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D153" s="6" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="154" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D154" s="6" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="155" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D155" s="6" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="156" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D156" s="6" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="157" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D157" s="6" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="158" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D158" s="6" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="160" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D160" s="6" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="162" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D162" s="6" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="164" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D164" s="6" t="s">
+        <v>560</v>
       </c>
     </row>
   </sheetData>
@@ -5600,7 +6343,7 @@
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4:E48">
+  <conditionalFormatting sqref="E4:E49">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="In Progress">
       <formula>NOT(ISERROR(SEARCH("In Progress",E4)))</formula>
     </cfRule>
@@ -5630,46 +6373,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="55" t="s">
-        <v>430</v>
-      </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
+      <c r="B1" s="56" t="s">
+        <v>391</v>
+      </c>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
     </row>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B2" s="58" t="s">
-        <v>431</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
+      <c r="B2" s="59" t="s">
+        <v>392</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
     </row>
     <row r="4" spans="2:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="59" t="s">
-        <v>432</v>
-      </c>
-      <c r="C4" s="59" t="s">
-        <v>433</v>
-      </c>
-      <c r="D4" s="59" t="s">
-        <v>434</v>
-      </c>
-      <c r="E4" s="59" t="s">
-        <v>435</v>
-      </c>
-      <c r="F4" s="59" t="s">
-        <v>436</v>
-      </c>
-      <c r="G4" s="59" t="s">
+      <c r="B4" s="43" t="s">
+        <v>393</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>395</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>396</v>
+      </c>
+      <c r="F4" s="43" t="s">
+        <v>397</v>
+      </c>
+      <c r="G4" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="59" t="s">
-        <v>437</v>
+      <c r="H4" s="43" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5677,22 +6420,22 @@
         <v>1</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>438</v>
+        <v>399</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>439</v>
-      </c>
-      <c r="E5" s="60" t="s">
-        <v>440</v>
-      </c>
-      <c r="F5" s="61" t="s">
-        <v>441</v>
-      </c>
-      <c r="G5" s="62">
+        <v>400</v>
+      </c>
+      <c r="E5" s="44" t="s">
+        <v>401</v>
+      </c>
+      <c r="F5" s="45" t="s">
+        <v>402</v>
+      </c>
+      <c r="G5" s="46">
         <v>6</v>
       </c>
-      <c r="H5" s="60" t="s">
-        <v>442</v>
+      <c r="H5" s="44" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -5700,20 +6443,20 @@
         <v>2</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>443</v>
+        <v>404</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>444</v>
-      </c>
-      <c r="E6" s="60" t="s">
-        <v>445</v>
-      </c>
-      <c r="F6" s="63" t="s">
-        <v>446</v>
-      </c>
-      <c r="G6" s="62"/>
-      <c r="H6" s="60" t="s">
-        <v>447</v>
+        <v>405</v>
+      </c>
+      <c r="E6" s="44" t="s">
+        <v>406</v>
+      </c>
+      <c r="F6" s="47" t="s">
+        <v>407</v>
+      </c>
+      <c r="G6" s="46"/>
+      <c r="H6" s="44" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -5721,22 +6464,22 @@
         <v>3</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>448</v>
+        <v>409</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>449</v>
-      </c>
-      <c r="E7" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="F7" s="63" t="s">
-        <v>446</v>
-      </c>
-      <c r="G7" s="62">
+        <v>410</v>
+      </c>
+      <c r="E7" s="44" t="s">
+        <v>411</v>
+      </c>
+      <c r="F7" s="47" t="s">
+        <v>407</v>
+      </c>
+      <c r="G7" s="46">
         <v>4</v>
       </c>
-      <c r="H7" s="60" t="s">
-        <v>442</v>
+      <c r="H7" s="44" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5744,22 +6487,22 @@
         <v>4</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>451</v>
+        <v>412</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>452</v>
-      </c>
-      <c r="E8" s="60" t="s">
-        <v>453</v>
-      </c>
-      <c r="F8" s="61" t="s">
-        <v>441</v>
-      </c>
-      <c r="G8" s="62">
+        <v>413</v>
+      </c>
+      <c r="E8" s="44" t="s">
+        <v>414</v>
+      </c>
+      <c r="F8" s="45" t="s">
+        <v>402</v>
+      </c>
+      <c r="G8" s="46">
         <v>8</v>
       </c>
-      <c r="H8" s="60" t="s">
-        <v>454</v>
+      <c r="H8" s="44" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -5767,22 +6510,22 @@
         <v>5</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>455</v>
+        <v>416</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>456</v>
-      </c>
-      <c r="E9" s="60" t="s">
-        <v>457</v>
-      </c>
-      <c r="F9" s="64" t="s">
-        <v>458</v>
-      </c>
-      <c r="G9" s="62">
+        <v>417</v>
+      </c>
+      <c r="E9" s="44" t="s">
+        <v>418</v>
+      </c>
+      <c r="F9" s="48" t="s">
+        <v>419</v>
+      </c>
+      <c r="G9" s="46">
         <v>2</v>
       </c>
-      <c r="H9" s="60" t="s">
-        <v>459</v>
+      <c r="H9" s="44" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5790,22 +6533,22 @@
         <v>6</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>460</v>
+        <v>421</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>461</v>
-      </c>
-      <c r="E10" s="60" t="s">
-        <v>462</v>
-      </c>
-      <c r="F10" s="63" t="s">
-        <v>446</v>
-      </c>
-      <c r="G10" s="62">
+        <v>422</v>
+      </c>
+      <c r="E10" s="44" t="s">
+        <v>423</v>
+      </c>
+      <c r="F10" s="47" t="s">
+        <v>407</v>
+      </c>
+      <c r="G10" s="46">
         <v>8</v>
       </c>
-      <c r="H10" s="60" t="s">
-        <v>459</v>
+      <c r="H10" s="44" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5813,22 +6556,22 @@
         <v>7</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>463</v>
+        <v>424</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>464</v>
-      </c>
-      <c r="E11" s="60" t="s">
-        <v>465</v>
-      </c>
-      <c r="F11" s="64" t="s">
-        <v>458</v>
-      </c>
-      <c r="G11" s="62">
+        <v>425</v>
+      </c>
+      <c r="E11" s="44" t="s">
+        <v>426</v>
+      </c>
+      <c r="F11" s="48" t="s">
+        <v>419</v>
+      </c>
+      <c r="G11" s="46">
         <v>2</v>
       </c>
-      <c r="H11" s="60" t="s">
-        <v>466</v>
+      <c r="H11" s="44" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="12" spans="2:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -5836,22 +6579,22 @@
         <v>8</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>467</v>
+        <v>428</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>468</v>
-      </c>
-      <c r="E12" s="60" t="s">
-        <v>469</v>
-      </c>
-      <c r="F12" s="63" t="s">
-        <v>446</v>
-      </c>
-      <c r="G12" s="62">
+        <v>429</v>
+      </c>
+      <c r="E12" s="44" t="s">
+        <v>430</v>
+      </c>
+      <c r="F12" s="47" t="s">
+        <v>407</v>
+      </c>
+      <c r="G12" s="46">
         <v>6</v>
       </c>
-      <c r="H12" s="60" t="s">
-        <v>459</v>
+      <c r="H12" s="44" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -5859,22 +6602,22 @@
         <v>9</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>470</v>
+        <v>431</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>471</v>
-      </c>
-      <c r="E13" s="60" t="s">
-        <v>472</v>
-      </c>
-      <c r="F13" s="64" t="s">
-        <v>458</v>
-      </c>
-      <c r="G13" s="62">
+        <v>432</v>
+      </c>
+      <c r="E13" s="44" t="s">
+        <v>433</v>
+      </c>
+      <c r="F13" s="48" t="s">
+        <v>419</v>
+      </c>
+      <c r="G13" s="46">
         <v>8</v>
       </c>
-      <c r="H13" s="60" t="s">
-        <v>473</v>
+      <c r="H13" s="44" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -5882,22 +6625,22 @@
         <v>10</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>474</v>
+        <v>435</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>475</v>
-      </c>
-      <c r="E14" s="60" t="s">
-        <v>476</v>
-      </c>
-      <c r="F14" s="64" t="s">
-        <v>458</v>
-      </c>
-      <c r="G14" s="62">
+        <v>436</v>
+      </c>
+      <c r="E14" s="44" t="s">
+        <v>437</v>
+      </c>
+      <c r="F14" s="48" t="s">
+        <v>419</v>
+      </c>
+      <c r="G14" s="46">
         <v>12</v>
       </c>
-      <c r="H14" s="60" t="s">
-        <v>473</v>
+      <c r="H14" s="44" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="36" customHeight="1" x14ac:dyDescent="0.3">
@@ -5905,22 +6648,22 @@
         <v>11</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>477</v>
+        <v>438</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>478</v>
-      </c>
-      <c r="E15" s="60" t="s">
-        <v>479</v>
-      </c>
-      <c r="F15" s="64" t="s">
-        <v>458</v>
-      </c>
-      <c r="G15" s="62">
+        <v>439</v>
+      </c>
+      <c r="E15" s="44" t="s">
+        <v>440</v>
+      </c>
+      <c r="F15" s="48" t="s">
+        <v>419</v>
+      </c>
+      <c r="G15" s="46">
         <v>16</v>
       </c>
-      <c r="H15" s="60" t="s">
-        <v>473</v>
+      <c r="H15" s="44" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="36" customHeight="1" x14ac:dyDescent="0.3">
@@ -5928,22 +6671,22 @@
         <v>12</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>480</v>
+        <v>441</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>481</v>
-      </c>
-      <c r="E16" s="60" t="s">
-        <v>482</v>
-      </c>
-      <c r="F16" s="64" t="s">
-        <v>458</v>
-      </c>
-      <c r="G16" s="62">
+        <v>442</v>
+      </c>
+      <c r="E16" s="44" t="s">
+        <v>443</v>
+      </c>
+      <c r="F16" s="48" t="s">
+        <v>419</v>
+      </c>
+      <c r="G16" s="46">
         <v>8</v>
       </c>
-      <c r="H16" s="60" t="s">
-        <v>473</v>
+      <c r="H16" s="44" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -5951,22 +6694,22 @@
         <v>13</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>483</v>
+        <v>444</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>484</v>
-      </c>
-      <c r="E17" s="60" t="s">
-        <v>485</v>
-      </c>
-      <c r="F17" s="64" t="s">
-        <v>458</v>
-      </c>
-      <c r="G17" s="62">
+        <v>445</v>
+      </c>
+      <c r="E17" s="44" t="s">
+        <v>446</v>
+      </c>
+      <c r="F17" s="48" t="s">
+        <v>419</v>
+      </c>
+      <c r="G17" s="46">
         <v>16</v>
       </c>
-      <c r="H17" s="60" t="s">
-        <v>473</v>
+      <c r="H17" s="44" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -5974,22 +6717,22 @@
         <v>14</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>486</v>
+        <v>447</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>487</v>
-      </c>
-      <c r="E18" s="60" t="s">
-        <v>488</v>
-      </c>
-      <c r="F18" s="63" t="s">
-        <v>446</v>
-      </c>
-      <c r="G18" s="62">
+        <v>448</v>
+      </c>
+      <c r="E18" s="44" t="s">
+        <v>449</v>
+      </c>
+      <c r="F18" s="47" t="s">
+        <v>407</v>
+      </c>
+      <c r="G18" s="46">
         <v>4</v>
       </c>
-      <c r="H18" s="60" t="s">
-        <v>459</v>
+      <c r="H18" s="44" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="36" customHeight="1" x14ac:dyDescent="0.3">
@@ -5997,22 +6740,22 @@
         <v>15</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>489</v>
+        <v>450</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>490</v>
-      </c>
-      <c r="E19" s="60" t="s">
-        <v>491</v>
-      </c>
-      <c r="F19" s="64" t="s">
-        <v>458</v>
-      </c>
-      <c r="G19" s="62">
+        <v>451</v>
+      </c>
+      <c r="E19" s="44" t="s">
+        <v>452</v>
+      </c>
+      <c r="F19" s="48" t="s">
+        <v>419</v>
+      </c>
+      <c r="G19" s="46">
         <v>4</v>
       </c>
-      <c r="H19" s="60" t="s">
-        <v>459</v>
+      <c r="H19" s="44" t="s">
+        <v>420</v>
       </c>
     </row>
   </sheetData>

--- a/REFM_Build_Prompts_v2.1.xlsx
+++ b/REFM_Build_Prompts_v2.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FMP\financial-modeler-pro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4A03F5-C04B-44F6-BE90-E520EB4574F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF20A0B-F023-4087-A648-378460BBCC26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Architecture" sheetId="1" r:id="rId1"/>
@@ -2149,7 +2149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2236,35 +2236,17 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2703,22 +2685,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="28.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="56" t="s">
+      <c r="B1" s="50" t="s">
         <v>194</v>
       </c>
-      <c r="C1" s="55"/>
+      <c r="C1" s="49"/>
     </row>
     <row r="2" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="53" t="s">
         <v>195</v>
       </c>
-      <c r="C2" s="55"/>
+      <c r="C2" s="49"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="45" t="s">
         <v>196</v>
       </c>
-      <c r="C4" s="52"/>
+      <c r="C4" s="46"/>
     </row>
     <row r="5" spans="2:3" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
@@ -2777,10 +2759,10 @@
       </c>
     </row>
     <row r="13" spans="2:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="51" t="s">
         <v>210</v>
       </c>
-      <c r="C13" s="58"/>
+      <c r="C13" s="52"/>
     </row>
     <row r="14" spans="2:3" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="28" t="s">
@@ -2823,10 +2805,10 @@
       </c>
     </row>
     <row r="19" spans="2:3" ht="97.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="53" t="s">
+      <c r="B19" s="47" t="s">
         <v>221</v>
       </c>
-      <c r="C19" s="54" t="s">
+      <c r="C19" s="48" t="s">
         <v>222</v>
       </c>
     </row>
@@ -2853,10 +2835,10 @@
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B23" s="49" t="s">
+      <c r="B23" s="43" t="s">
         <v>228</v>
       </c>
-      <c r="C23" s="50" t="s">
+      <c r="C23" s="44" t="s">
         <v>229</v>
       </c>
     </row>
@@ -2900,8 +2882,8 @@
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B30" s="55"/>
-      <c r="C30" s="55"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="49"/>
     </row>
     <row r="31" spans="2:3" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="26" t="s">
@@ -2950,10 +2932,10 @@
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B38" s="51" t="s">
+      <c r="B38" s="45" t="s">
         <v>250</v>
       </c>
-      <c r="C38" s="52"/>
+      <c r="C38" s="46"/>
     </row>
     <row r="39" spans="2:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
@@ -3035,10 +3017,10 @@
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B50" s="49" t="s">
+      <c r="B50" s="43" t="s">
         <v>269</v>
       </c>
-      <c r="C50" s="50" t="s">
+      <c r="C50" s="44" t="s">
         <v>270</v>
       </c>
     </row>
@@ -3083,10 +3065,10 @@
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B56" s="49" t="s">
+      <c r="B56" s="43" t="s">
         <v>281</v>
       </c>
-      <c r="C56" s="50" t="s">
+      <c r="C56" s="44" t="s">
         <v>282</v>
       </c>
     </row>
@@ -3130,8 +3112,8 @@
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B63" s="55"/>
-      <c r="C63" s="55"/>
+      <c r="B63" s="49"/>
+      <c r="C63" s="49"/>
     </row>
     <row r="64" spans="2:3" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="26" t="s">
@@ -3172,10 +3154,10 @@
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B69" s="49" t="s">
+      <c r="B69" s="43" t="s">
         <v>301</v>
       </c>
-      <c r="C69" s="50" t="s">
+      <c r="C69" s="44" t="s">
         <v>302</v>
       </c>
     </row>
@@ -3219,8 +3201,8 @@
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B76" s="55"/>
-      <c r="C76" s="55"/>
+      <c r="B76" s="49"/>
+      <c r="C76" s="49"/>
     </row>
     <row r="77" spans="2:3" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="26" t="s">
@@ -3269,10 +3251,10 @@
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B84" s="51" t="s">
+      <c r="B84" s="45" t="s">
         <v>323</v>
       </c>
-      <c r="C84" s="52"/>
+      <c r="C84" s="46"/>
     </row>
     <row r="85" spans="2:3" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
@@ -3315,10 +3297,10 @@
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B90" s="49" t="s">
+      <c r="B90" s="43" t="s">
         <v>334</v>
       </c>
-      <c r="C90" s="50" t="s">
+      <c r="C90" s="44" t="s">
         <v>335</v>
       </c>
     </row>
@@ -3346,10 +3328,10 @@
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B95" s="49" t="s">
+      <c r="B95" s="43" t="s">
         <v>341</v>
       </c>
-      <c r="C95" s="50" t="s">
+      <c r="C95" s="44" t="s">
         <v>342</v>
       </c>
     </row>
@@ -3377,10 +3359,10 @@
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B100" s="49" t="s">
+      <c r="B100" s="43" t="s">
         <v>348</v>
       </c>
-      <c r="C100" s="50" t="s">
+      <c r="C100" s="44" t="s">
         <v>349</v>
       </c>
     </row>
@@ -3519,31 +3501,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="60" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
+      <c r="B1" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
       <c r="K1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
       <c r="K2" s="6" t="s">
         <v>3</v>
       </c>
@@ -3786,16 +3768,16 @@
       </c>
     </row>
     <row r="15" spans="2:11" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="15" t="s">
         <v>1</v>
       </c>
       <c r="F15" s="23">
@@ -3804,24 +3786,24 @@
       <c r="G15" s="23">
         <v>46144</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="9">
         <v>12</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="8" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="16" spans="2:11" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="15" t="s">
         <v>1</v>
       </c>
       <c r="F16" s="23">
@@ -3830,24 +3812,24 @@
       <c r="G16" s="23">
         <v>46144</v>
       </c>
-      <c r="H16" s="39">
+      <c r="H16" s="9">
         <v>6</v>
       </c>
-      <c r="I16" s="38" t="s">
+      <c r="I16" s="8" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="15" t="s">
         <v>1</v>
       </c>
       <c r="F17" s="23">
@@ -3856,24 +3838,24 @@
       <c r="G17" s="23">
         <v>46144</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="9">
         <v>6</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="8" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="29" t="s">
+      <c r="D18" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="15" t="s">
         <v>1</v>
       </c>
       <c r="F18" s="23">
@@ -3882,32 +3864,36 @@
       <c r="G18" s="23">
         <v>46144</v>
       </c>
-      <c r="H18" s="31">
+      <c r="H18" s="9">
         <v>16</v>
       </c>
-      <c r="I18" s="29" t="s">
+      <c r="I18" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="8" t="s">
         <v>454</v>
       </c>
-      <c r="D19" s="29" t="s">
+      <c r="D19" s="8" t="s">
         <v>455</v>
       </c>
-      <c r="E19" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="31">
+      <c r="E19" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="23">
+        <v>46145</v>
+      </c>
+      <c r="G19" s="23">
+        <v>46145</v>
+      </c>
+      <c r="H19" s="9">
         <v>8</v>
       </c>
-      <c r="I19" s="29" t="s">
+      <c r="I19" s="8" t="s">
         <v>54</v>
       </c>
     </row>
@@ -4840,24 +4826,24 @@
     <col min="3" max="3" width="32" style="6" customWidth="1"/>
     <col min="4" max="4" width="110" style="6" customWidth="1"/>
     <col min="5" max="5" width="11.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="35" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="35"/>
+    <col min="6" max="6" width="8.88671875" style="32" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="32"/>
     <col min="8" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="54" t="s">
         <v>372</v>
       </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
     </row>
     <row r="2" spans="2:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="58" t="s">
         <v>373</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
     </row>
     <row r="4" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
@@ -4872,10 +4858,10 @@
       <c r="E4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="36" t="s">
+      <c r="G4" s="33" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4893,11 +4879,11 @@
         <f>Tracker!E14</f>
         <v xml:space="preserve">Done </v>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="32">
         <f>Tracker!F14</f>
         <v>46144</v>
       </c>
-      <c r="G5" s="35">
+      <c r="G5" s="32">
         <f>Tracker!G14</f>
         <v>46144</v>
       </c>
@@ -4916,34 +4902,34 @@
         <f>Tracker!E15</f>
         <v xml:space="preserve">Done </v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="32">
         <f>Tracker!F15</f>
         <v>46144</v>
       </c>
-      <c r="G6" s="35">
+      <c r="G6" s="32">
         <f>Tracker!G15</f>
         <v>46144</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="34" t="s">
         <v>386</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="35" t="s">
         <v>387</v>
       </c>
-      <c r="D7" s="42" t="s">
+      <c r="D7" s="36" t="s">
         <v>390</v>
       </c>
       <c r="E7" s="15" t="str">
         <f>Tracker!E16</f>
         <v xml:space="preserve">Done </v>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="32">
         <f>Tracker!F16</f>
         <v>46144</v>
       </c>
-      <c r="G7" s="35">
+      <c r="G7" s="32">
         <f>Tracker!G16</f>
         <v>46144</v>
       </c>
@@ -4960,59 +4946,59 @@
         <f>Tracker!E17</f>
         <v xml:space="preserve">Done </v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="32">
         <f>Tracker!F17</f>
         <v>46144</v>
       </c>
-      <c r="G8" s="35">
+      <c r="G8" s="32">
         <f>Tracker!G17</f>
         <v>46144</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="31" t="s">
         <v>389</v>
       </c>
       <c r="E9" s="15" t="str">
         <f>Tracker!E18</f>
         <v xml:space="preserve">Done </v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="32">
         <f>Tracker!F18</f>
         <v>46144</v>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="32">
         <f>Tracker!G18</f>
         <v>46144</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="30" t="s">
         <v>453</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="30" t="s">
         <v>454</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="31" t="s">
         <v>561</v>
       </c>
       <c r="E10" s="15" t="str">
         <f>Tracker!E19</f>
-        <v>Not Started</v>
-      </c>
-      <c r="F10" s="35">
+        <v xml:space="preserve">Done </v>
+      </c>
+      <c r="F10" s="32">
         <f>Tracker!F19</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="35">
+        <v>46145</v>
+      </c>
+      <c r="G10" s="32">
         <f>Tracker!G19</f>
-        <v>0</v>
+        <v>46145</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -5027,11 +5013,11 @@
         <f>Tracker!E20</f>
         <v>Not started</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="32">
         <f>Tracker!F20</f>
         <v>0</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="32">
         <f>Tracker!G20</f>
         <v>0</v>
       </c>
@@ -5050,11 +5036,11 @@
         <f>Tracker!E21</f>
         <v>Not started</v>
       </c>
-      <c r="F12" s="35">
+      <c r="F12" s="32">
         <f>Tracker!F21</f>
         <v>0</v>
       </c>
-      <c r="G12" s="35">
+      <c r="G12" s="32">
         <f>Tracker!G21</f>
         <v>0</v>
       </c>
@@ -5071,11 +5057,11 @@
         <f>Tracker!E22</f>
         <v>Not started</v>
       </c>
-      <c r="F13" s="35">
+      <c r="F13" s="32">
         <f>Tracker!F22</f>
         <v>0</v>
       </c>
-      <c r="G13" s="35">
+      <c r="G13" s="32">
         <f>Tracker!G22</f>
         <v>0</v>
       </c>
@@ -5094,11 +5080,11 @@
         <f>Tracker!E23</f>
         <v>Not started</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="32">
         <f>Tracker!F23</f>
         <v>0</v>
       </c>
-      <c r="G14" s="35">
+      <c r="G14" s="32">
         <f>Tracker!G23</f>
         <v>0</v>
       </c>
@@ -5115,11 +5101,11 @@
         <f>Tracker!E24</f>
         <v>Not started</v>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="32">
         <f>Tracker!F24</f>
         <v>0</v>
       </c>
-      <c r="G15" s="35">
+      <c r="G15" s="32">
         <f>Tracker!G24</f>
         <v>0</v>
       </c>
@@ -5138,11 +5124,11 @@
         <f>Tracker!E25</f>
         <v>Not started</v>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="32">
         <f>Tracker!F25</f>
         <v>0</v>
       </c>
-      <c r="G16" s="35">
+      <c r="G16" s="32">
         <f>Tracker!G25</f>
         <v>0</v>
       </c>
@@ -5159,11 +5145,11 @@
         <f>Tracker!E26</f>
         <v>Not started</v>
       </c>
-      <c r="F17" s="35">
+      <c r="F17" s="32">
         <f>Tracker!F26</f>
         <v>0</v>
       </c>
-      <c r="G17" s="35">
+      <c r="G17" s="32">
         <f>Tracker!G26</f>
         <v>0</v>
       </c>
@@ -5182,11 +5168,11 @@
         <f>Tracker!E27</f>
         <v>Not started</v>
       </c>
-      <c r="F18" s="35">
+      <c r="F18" s="32">
         <f>Tracker!F27</f>
         <v>0</v>
       </c>
-      <c r="G18" s="35">
+      <c r="G18" s="32">
         <f>Tracker!G27</f>
         <v>0</v>
       </c>
@@ -5203,11 +5189,11 @@
         <f>Tracker!E28</f>
         <v>Not started</v>
       </c>
-      <c r="F19" s="35">
+      <c r="F19" s="32">
         <f>Tracker!F28</f>
         <v>0</v>
       </c>
-      <c r="G19" s="35">
+      <c r="G19" s="32">
         <f>Tracker!G28</f>
         <v>0</v>
       </c>
@@ -5226,11 +5212,11 @@
         <f>Tracker!E29</f>
         <v>Not started</v>
       </c>
-      <c r="F20" s="35">
+      <c r="F20" s="32">
         <f>Tracker!F29</f>
         <v>0</v>
       </c>
-      <c r="G20" s="35">
+      <c r="G20" s="32">
         <f>Tracker!G29</f>
         <v>0</v>
       </c>
@@ -5247,11 +5233,11 @@
         <f>Tracker!E30</f>
         <v>Not started</v>
       </c>
-      <c r="F21" s="35">
+      <c r="F21" s="32">
         <f>Tracker!F30</f>
         <v>0</v>
       </c>
-      <c r="G21" s="35">
+      <c r="G21" s="32">
         <f>Tracker!G30</f>
         <v>0</v>
       </c>
@@ -5270,11 +5256,11 @@
         <f>Tracker!E31</f>
         <v>Not started</v>
       </c>
-      <c r="F22" s="35">
+      <c r="F22" s="32">
         <f>Tracker!F31</f>
         <v>0</v>
       </c>
-      <c r="G22" s="35">
+      <c r="G22" s="32">
         <f>Tracker!G31</f>
         <v>0</v>
       </c>
@@ -5291,11 +5277,11 @@
         <f>Tracker!E32</f>
         <v>Not started</v>
       </c>
-      <c r="F23" s="35">
+      <c r="F23" s="32">
         <f>Tracker!F32</f>
         <v>0</v>
       </c>
-      <c r="G23" s="35">
+      <c r="G23" s="32">
         <f>Tracker!G32</f>
         <v>0</v>
       </c>
@@ -5314,11 +5300,11 @@
         <f>Tracker!E33</f>
         <v>Not started</v>
       </c>
-      <c r="F24" s="35">
+      <c r="F24" s="32">
         <f>Tracker!F33</f>
         <v>0</v>
       </c>
-      <c r="G24" s="35">
+      <c r="G24" s="32">
         <f>Tracker!G33</f>
         <v>0</v>
       </c>
@@ -5335,11 +5321,11 @@
         <f>Tracker!E34</f>
         <v>Not started</v>
       </c>
-      <c r="F25" s="35">
+      <c r="F25" s="32">
         <f>Tracker!F34</f>
         <v>0</v>
       </c>
-      <c r="G25" s="35">
+      <c r="G25" s="32">
         <f>Tracker!G34</f>
         <v>0</v>
       </c>
@@ -5358,11 +5344,11 @@
         <f>Tracker!E35</f>
         <v>Not started</v>
       </c>
-      <c r="F26" s="35">
+      <c r="F26" s="32">
         <f>Tracker!F35</f>
         <v>0</v>
       </c>
-      <c r="G26" s="35">
+      <c r="G26" s="32">
         <f>Tracker!G35</f>
         <v>0</v>
       </c>
@@ -5379,11 +5365,11 @@
         <f>Tracker!E36</f>
         <v>Not started</v>
       </c>
-      <c r="F27" s="35">
+      <c r="F27" s="32">
         <f>Tracker!F36</f>
         <v>0</v>
       </c>
-      <c r="G27" s="35">
+      <c r="G27" s="32">
         <f>Tracker!G36</f>
         <v>0</v>
       </c>
@@ -5402,11 +5388,11 @@
         <f>Tracker!E37</f>
         <v>Not started</v>
       </c>
-      <c r="F28" s="35">
+      <c r="F28" s="32">
         <f>Tracker!F37</f>
         <v>0</v>
       </c>
-      <c r="G28" s="35">
+      <c r="G28" s="32">
         <f>Tracker!G37</f>
         <v>0</v>
       </c>
@@ -5423,11 +5409,11 @@
         <f>Tracker!E38</f>
         <v>Not started</v>
       </c>
-      <c r="F29" s="35">
+      <c r="F29" s="32">
         <f>Tracker!F38</f>
         <v>0</v>
       </c>
-      <c r="G29" s="35">
+      <c r="G29" s="32">
         <f>Tracker!G38</f>
         <v>0</v>
       </c>
@@ -5446,11 +5432,11 @@
         <f>Tracker!E39</f>
         <v>Not started</v>
       </c>
-      <c r="F30" s="35">
+      <c r="F30" s="32">
         <f>Tracker!F39</f>
         <v>0</v>
       </c>
-      <c r="G30" s="35">
+      <c r="G30" s="32">
         <f>Tracker!G39</f>
         <v>0</v>
       </c>
@@ -5467,11 +5453,11 @@
         <f>Tracker!E40</f>
         <v>Not started</v>
       </c>
-      <c r="F31" s="35">
+      <c r="F31" s="32">
         <f>Tracker!F40</f>
         <v>0</v>
       </c>
-      <c r="G31" s="35">
+      <c r="G31" s="32">
         <f>Tracker!G40</f>
         <v>0</v>
       </c>
@@ -5490,11 +5476,11 @@
         <f>Tracker!E41</f>
         <v>Not started</v>
       </c>
-      <c r="F32" s="35">
+      <c r="F32" s="32">
         <f>Tracker!F41</f>
         <v>0</v>
       </c>
-      <c r="G32" s="35">
+      <c r="G32" s="32">
         <f>Tracker!G41</f>
         <v>0</v>
       </c>
@@ -5511,11 +5497,11 @@
         <f>Tracker!E42</f>
         <v>Not started</v>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="32">
         <f>Tracker!F42</f>
         <v>0</v>
       </c>
-      <c r="G33" s="35">
+      <c r="G33" s="32">
         <f>Tracker!G42</f>
         <v>0</v>
       </c>
@@ -5534,11 +5520,11 @@
         <f>Tracker!E43</f>
         <v>Not started</v>
       </c>
-      <c r="F34" s="35">
+      <c r="F34" s="32">
         <f>Tracker!F43</f>
         <v>0</v>
       </c>
-      <c r="G34" s="35">
+      <c r="G34" s="32">
         <f>Tracker!G43</f>
         <v>0</v>
       </c>
@@ -5558,11 +5544,11 @@
         <f>Tracker!E44</f>
         <v>Not started</v>
       </c>
-      <c r="F35" s="35">
+      <c r="F35" s="32">
         <f>Tracker!F44</f>
         <v>0</v>
       </c>
-      <c r="G35" s="35">
+      <c r="G35" s="32">
         <f>Tracker!G44</f>
         <v>0</v>
       </c>
@@ -5581,11 +5567,11 @@
         <f>Tracker!E45</f>
         <v>Optional v1.5</v>
       </c>
-      <c r="F36" s="35">
+      <c r="F36" s="32">
         <f>Tracker!F45</f>
         <v>0</v>
       </c>
-      <c r="G36" s="35">
+      <c r="G36" s="32">
         <f>Tracker!G45</f>
         <v>0</v>
       </c>
@@ -5605,11 +5591,11 @@
         <f>Tracker!E46</f>
         <v>Not started</v>
       </c>
-      <c r="F37" s="35">
+      <c r="F37" s="32">
         <f>Tracker!F46</f>
         <v>0</v>
       </c>
-      <c r="G37" s="35">
+      <c r="G37" s="32">
         <f>Tracker!G46</f>
         <v>0</v>
       </c>
@@ -5628,11 +5614,11 @@
         <f>Tracker!E47</f>
         <v>Not started</v>
       </c>
-      <c r="F38" s="35">
+      <c r="F38" s="32">
         <f>Tracker!F47</f>
         <v>0</v>
       </c>
-      <c r="G38" s="35">
+      <c r="G38" s="32">
         <f>Tracker!G47</f>
         <v>0</v>
       </c>
@@ -5651,11 +5637,11 @@
         <f>Tracker!E48</f>
         <v>Not started</v>
       </c>
-      <c r="F39" s="35">
+      <c r="F39" s="32">
         <f>Tracker!F48</f>
         <v>0</v>
       </c>
-      <c r="G39" s="35">
+      <c r="G39" s="32">
         <f>Tracker!G48</f>
         <v>0</v>
       </c>
@@ -5674,11 +5660,11 @@
         <f>Tracker!E49</f>
         <v>Not started</v>
       </c>
-      <c r="F40" s="35">
+      <c r="F40" s="32">
         <f>Tracker!F49</f>
         <v>0</v>
       </c>
-      <c r="G40" s="35">
+      <c r="G40" s="32">
         <f>Tracker!G49</f>
         <v>0</v>
       </c>
@@ -5695,11 +5681,11 @@
         <f>Tracker!E50</f>
         <v>Not started</v>
       </c>
-      <c r="F41" s="35">
+      <c r="F41" s="32">
         <f>Tracker!F50</f>
         <v>0</v>
       </c>
-      <c r="G41" s="35">
+      <c r="G41" s="32">
         <f>Tracker!G50</f>
         <v>0</v>
       </c>
@@ -5718,11 +5704,11 @@
         <f>Tracker!E51</f>
         <v>Not started</v>
       </c>
-      <c r="F42" s="35">
+      <c r="F42" s="32">
         <f>Tracker!F51</f>
         <v>0</v>
       </c>
-      <c r="G42" s="35">
+      <c r="G42" s="32">
         <f>Tracker!G51</f>
         <v>0</v>
       </c>
@@ -5739,11 +5725,11 @@
         <f>Tracker!E52</f>
         <v>Not started</v>
       </c>
-      <c r="F43" s="35">
+      <c r="F43" s="32">
         <f>Tracker!F52</f>
         <v>0</v>
       </c>
-      <c r="G43" s="35">
+      <c r="G43" s="32">
         <f>Tracker!G52</f>
         <v>0</v>
       </c>
@@ -5762,11 +5748,11 @@
         <f>Tracker!E53</f>
         <v>Not started</v>
       </c>
-      <c r="F44" s="35">
+      <c r="F44" s="32">
         <f>Tracker!F53</f>
         <v>0</v>
       </c>
-      <c r="G44" s="35">
+      <c r="G44" s="32">
         <f>Tracker!G53</f>
         <v>0</v>
       </c>
@@ -5783,11 +5769,11 @@
         <f>Tracker!E54</f>
         <v>Not started</v>
       </c>
-      <c r="F45" s="35">
+      <c r="F45" s="32">
         <f>Tracker!F54</f>
         <v>0</v>
       </c>
-      <c r="G45" s="35">
+      <c r="G45" s="32">
         <f>Tracker!G54</f>
         <v>0</v>
       </c>
@@ -5806,11 +5792,11 @@
         <f>Tracker!E55</f>
         <v>Not started</v>
       </c>
-      <c r="F46" s="35">
+      <c r="F46" s="32">
         <f>Tracker!F55</f>
         <v>0</v>
       </c>
-      <c r="G46" s="35">
+      <c r="G46" s="32">
         <f>Tracker!G55</f>
         <v>0</v>
       </c>
@@ -5827,11 +5813,11 @@
         <f>Tracker!E56</f>
         <v>Not started</v>
       </c>
-      <c r="F47" s="35">
+      <c r="F47" s="32">
         <f>Tracker!F56</f>
         <v>0</v>
       </c>
-      <c r="G47" s="35">
+      <c r="G47" s="32">
         <f>Tracker!G56</f>
         <v>0</v>
       </c>
@@ -5850,11 +5836,11 @@
         <f>Tracker!E57</f>
         <v>Not started</v>
       </c>
-      <c r="F48" s="35">
+      <c r="F48" s="32">
         <f>Tracker!F57</f>
         <v>0</v>
       </c>
-      <c r="G48" s="35">
+      <c r="G48" s="32">
         <f>Tracker!G57</f>
         <v>0</v>
       </c>
@@ -5874,11 +5860,11 @@
         <f>Tracker!E58</f>
         <v>Not started</v>
       </c>
-      <c r="F49" s="35">
+      <c r="F49" s="32">
         <f>Tracker!F58</f>
         <v>0</v>
       </c>
-      <c r="G49" s="35">
+      <c r="G49" s="32">
         <f>Tracker!G58</f>
         <v>0</v>
       </c>
@@ -6373,388 +6359,388 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="56" t="s">
+      <c r="B1" s="50" t="s">
         <v>391</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
     </row>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="53" t="s">
         <v>392</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
     </row>
     <row r="4" spans="2:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="37" t="s">
         <v>393</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="37" t="s">
         <v>394</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="37" t="s">
         <v>395</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="37" t="s">
         <v>396</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="F4" s="37" t="s">
         <v>397</v>
       </c>
-      <c r="G4" s="43" t="s">
+      <c r="G4" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="43" t="s">
+      <c r="H4" s="37" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="32">
+      <c r="B5" s="30">
         <v>1</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="30" t="s">
         <v>399</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="30" t="s">
         <v>400</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="38" t="s">
         <v>401</v>
       </c>
-      <c r="F5" s="45" t="s">
+      <c r="F5" s="39" t="s">
         <v>402</v>
       </c>
-      <c r="G5" s="46">
+      <c r="G5" s="40">
         <v>6</v>
       </c>
-      <c r="H5" s="44" t="s">
+      <c r="H5" s="38" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="32">
+      <c r="B6" s="30">
         <v>2</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="30" t="s">
         <v>404</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="30" t="s">
         <v>405</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="38" t="s">
         <v>406</v>
       </c>
-      <c r="F6" s="47" t="s">
+      <c r="F6" s="41" t="s">
         <v>407</v>
       </c>
-      <c r="G6" s="46"/>
-      <c r="H6" s="44" t="s">
+      <c r="G6" s="40"/>
+      <c r="H6" s="38" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="32">
+      <c r="B7" s="30">
         <v>3</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="30" t="s">
         <v>409</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="30" t="s">
         <v>410</v>
       </c>
-      <c r="E7" s="44" t="s">
+      <c r="E7" s="38" t="s">
         <v>411</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="41" t="s">
         <v>407</v>
       </c>
-      <c r="G7" s="46">
+      <c r="G7" s="40">
         <v>4</v>
       </c>
-      <c r="H7" s="44" t="s">
+      <c r="H7" s="38" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="32">
+      <c r="B8" s="30">
         <v>4</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="30" t="s">
         <v>412</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="30" t="s">
         <v>413</v>
       </c>
-      <c r="E8" s="44" t="s">
+      <c r="E8" s="38" t="s">
         <v>414</v>
       </c>
-      <c r="F8" s="45" t="s">
+      <c r="F8" s="39" t="s">
         <v>402</v>
       </c>
-      <c r="G8" s="46">
+      <c r="G8" s="40">
         <v>8</v>
       </c>
-      <c r="H8" s="44" t="s">
+      <c r="H8" s="38" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="32">
+      <c r="B9" s="30">
         <v>5</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="30" t="s">
         <v>416</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="30" t="s">
         <v>417</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="38" t="s">
         <v>418</v>
       </c>
-      <c r="F9" s="48" t="s">
+      <c r="F9" s="42" t="s">
         <v>419</v>
       </c>
-      <c r="G9" s="46">
+      <c r="G9" s="40">
         <v>2</v>
       </c>
-      <c r="H9" s="44" t="s">
+      <c r="H9" s="38" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="32">
+      <c r="B10" s="30">
         <v>6</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="30" t="s">
         <v>421</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="30" t="s">
         <v>422</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="38" t="s">
         <v>423</v>
       </c>
-      <c r="F10" s="47" t="s">
+      <c r="F10" s="41" t="s">
         <v>407</v>
       </c>
-      <c r="G10" s="46">
+      <c r="G10" s="40">
         <v>8</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="H10" s="38" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="32">
+      <c r="B11" s="30">
         <v>7</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="30" t="s">
         <v>424</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="30" t="s">
         <v>425</v>
       </c>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="38" t="s">
         <v>426</v>
       </c>
-      <c r="F11" s="48" t="s">
+      <c r="F11" s="42" t="s">
         <v>419</v>
       </c>
-      <c r="G11" s="46">
+      <c r="G11" s="40">
         <v>2</v>
       </c>
-      <c r="H11" s="44" t="s">
+      <c r="H11" s="38" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="12" spans="2:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="32">
+      <c r="B12" s="30">
         <v>8</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="30" t="s">
         <v>428</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="30" t="s">
         <v>429</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="38" t="s">
         <v>430</v>
       </c>
-      <c r="F12" s="47" t="s">
+      <c r="F12" s="41" t="s">
         <v>407</v>
       </c>
-      <c r="G12" s="46">
+      <c r="G12" s="40">
         <v>6</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="38" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="32">
+      <c r="B13" s="30">
         <v>9</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="30" t="s">
         <v>431</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="30" t="s">
         <v>432</v>
       </c>
-      <c r="E13" s="44" t="s">
+      <c r="E13" s="38" t="s">
         <v>433</v>
       </c>
-      <c r="F13" s="48" t="s">
+      <c r="F13" s="42" t="s">
         <v>419</v>
       </c>
-      <c r="G13" s="46">
+      <c r="G13" s="40">
         <v>8</v>
       </c>
-      <c r="H13" s="44" t="s">
+      <c r="H13" s="38" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="32">
+      <c r="B14" s="30">
         <v>10</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="30" t="s">
         <v>435</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="30" t="s">
         <v>436</v>
       </c>
-      <c r="E14" s="44" t="s">
+      <c r="E14" s="38" t="s">
         <v>437</v>
       </c>
-      <c r="F14" s="48" t="s">
+      <c r="F14" s="42" t="s">
         <v>419</v>
       </c>
-      <c r="G14" s="46">
+      <c r="G14" s="40">
         <v>12</v>
       </c>
-      <c r="H14" s="44" t="s">
+      <c r="H14" s="38" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="32">
+      <c r="B15" s="30">
         <v>11</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="30" t="s">
         <v>438</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="30" t="s">
         <v>439</v>
       </c>
-      <c r="E15" s="44" t="s">
+      <c r="E15" s="38" t="s">
         <v>440</v>
       </c>
-      <c r="F15" s="48" t="s">
+      <c r="F15" s="42" t="s">
         <v>419</v>
       </c>
-      <c r="G15" s="46">
+      <c r="G15" s="40">
         <v>16</v>
       </c>
-      <c r="H15" s="44" t="s">
+      <c r="H15" s="38" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="32">
+      <c r="B16" s="30">
         <v>12</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="30" t="s">
         <v>441</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="30" t="s">
         <v>442</v>
       </c>
-      <c r="E16" s="44" t="s">
+      <c r="E16" s="38" t="s">
         <v>443</v>
       </c>
-      <c r="F16" s="48" t="s">
+      <c r="F16" s="42" t="s">
         <v>419</v>
       </c>
-      <c r="G16" s="46">
+      <c r="G16" s="40">
         <v>8</v>
       </c>
-      <c r="H16" s="44" t="s">
+      <c r="H16" s="38" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="32">
+      <c r="B17" s="30">
         <v>13</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="30" t="s">
         <v>444</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="30" t="s">
         <v>445</v>
       </c>
-      <c r="E17" s="44" t="s">
+      <c r="E17" s="38" t="s">
         <v>446</v>
       </c>
-      <c r="F17" s="48" t="s">
+      <c r="F17" s="42" t="s">
         <v>419</v>
       </c>
-      <c r="G17" s="46">
+      <c r="G17" s="40">
         <v>16</v>
       </c>
-      <c r="H17" s="44" t="s">
+      <c r="H17" s="38" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="32">
+      <c r="B18" s="30">
         <v>14</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="30" t="s">
         <v>447</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="30" t="s">
         <v>448</v>
       </c>
-      <c r="E18" s="44" t="s">
+      <c r="E18" s="38" t="s">
         <v>449</v>
       </c>
-      <c r="F18" s="47" t="s">
+      <c r="F18" s="41" t="s">
         <v>407</v>
       </c>
-      <c r="G18" s="46">
+      <c r="G18" s="40">
         <v>4</v>
       </c>
-      <c r="H18" s="44" t="s">
+      <c r="H18" s="38" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="32">
+      <c r="B19" s="30">
         <v>15</v>
       </c>
-      <c r="C19" s="32" t="s">
+      <c r="C19" s="30" t="s">
         <v>450</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="30" t="s">
         <v>451</v>
       </c>
-      <c r="E19" s="44" t="s">
+      <c r="E19" s="38" t="s">
         <v>452</v>
       </c>
-      <c r="F19" s="48" t="s">
+      <c r="F19" s="42" t="s">
         <v>419</v>
       </c>
-      <c r="G19" s="46">
+      <c r="G19" s="40">
         <v>4</v>
       </c>
-      <c r="H19" s="44" t="s">
+      <c r="H19" s="38" t="s">
         <v>420</v>
       </c>
     </row>
